--- a/salidas/empresas/MRK.xlsx
+++ b/salidas/empresas/MRK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>15.93143463134766</v>
+        <v>15.93143653869629</v>
       </c>
       <c r="C2" t="n">
         <v>32.91984558105469</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>16.09768295288086</v>
+        <v>16.09768104553223</v>
       </c>
       <c r="C3" t="n">
         <v>33.26335906982422</v>
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>15.72218608856201</v>
+        <v>15.72218894958496</v>
       </c>
       <c r="C6" t="n">
         <v>31.76526641845703</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>17.20514106750488</v>
+        <v>17.20513916015625</v>
       </c>
       <c r="C7" t="n">
         <v>34.76145172119141</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>19.0186939239502</v>
+        <v>19.01869964599609</v>
       </c>
       <c r="C8" t="n">
         <v>38.42557144165039</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>19.32890892028809</v>
+        <v>19.32891464233398</v>
       </c>
       <c r="C9" t="n">
         <v>38.6927490234375</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>19.97241592407227</v>
+        <v>19.97240447998047</v>
       </c>
       <c r="C10" t="n">
         <v>39.98091506958008</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>21.65029144287109</v>
+        <v>21.65027809143066</v>
       </c>
       <c r="C11" t="n">
         <v>43.33969497680664</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>21.21652221679688</v>
+        <v>21.21651077270508</v>
       </c>
       <c r="C12" t="n">
         <v>42.47137451171875</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.95821380615234</v>
+        <v>20.95820426940918</v>
       </c>
       <c r="C13" t="n">
         <v>41.60305404663086</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>21.51099967956543</v>
+        <v>21.51100540161133</v>
       </c>
       <c r="C14" t="n">
         <v>42.70038223266602</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>21.22260093688965</v>
+        <v>21.22259140014648</v>
       </c>
       <c r="C15" t="n">
         <v>42.12786483764648</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>21.41437149047852</v>
+        <v>21.41436958312988</v>
       </c>
       <c r="C16" t="n">
         <v>42.14694595336914</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>24.93899726867676</v>
+        <v>24.93898773193359</v>
       </c>
       <c r="C17" t="n">
         <v>49.08396911621094</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>25.42865562438965</v>
+        <v>25.42867469787598</v>
       </c>
       <c r="C18" t="n">
         <v>50.04771041870117</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>24.32358169555664</v>
+        <v>24.32358741760254</v>
       </c>
       <c r="C19" t="n">
         <v>47.51908493041992</v>
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>24.50428771972656</v>
+        <v>24.50429916381836</v>
       </c>
       <c r="C21" t="n">
         <v>47.87213516235352</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>25.43988990783691</v>
+        <v>25.43988800048828</v>
       </c>
       <c r="C22" t="n">
         <v>49.32251739501953</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.67338943481445</v>
+        <v>28.67339706420898</v>
       </c>
       <c r="C23" t="n">
         <v>55.59160232543945</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>29.21477127075195</v>
+        <v>29.21476173400879</v>
       </c>
       <c r="C24" t="n">
         <v>56.64122009277344</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>28.78692245483398</v>
+        <v>28.78691673278809</v>
       </c>
       <c r="C25" t="n">
         <v>55.4484748840332</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>22.83732795715332</v>
+        <v>22.83732414245605</v>
       </c>
       <c r="C26" t="n">
         <v>43.98854827880859</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>21.94562339782715</v>
+        <v>21.94563293457031</v>
       </c>
       <c r="C27" t="n">
         <v>42.27099227905273</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>18.96460914611816</v>
+        <v>18.96460151672363</v>
       </c>
       <c r="C28" t="n">
         <v>36.21183013916016</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>19.00957870483398</v>
+        <v>19.00958633422852</v>
       </c>
       <c r="C29" t="n">
         <v>36.29771041870117</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>19.46932411193848</v>
+        <v>19.46932792663574</v>
       </c>
       <c r="C30" t="n">
         <v>37.17557144165039</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>19.02317428588867</v>
+        <v>19.02317237854004</v>
       </c>
       <c r="C31" t="n">
         <v>35.96374130249023</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>16.60552978515625</v>
+        <v>16.60552787780762</v>
       </c>
       <c r="C32" t="n">
         <v>31.39312934875488</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>18.00362396240234</v>
+        <v>18.00362014770508</v>
       </c>
       <c r="C33" t="n">
         <v>34.03625869750977</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>16.10490226745605</v>
+        <v>16.10489463806152</v>
       </c>
       <c r="C34" t="n">
         <v>30.11450386047363</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>15.79361438751221</v>
+        <v>15.79360771179199</v>
       </c>
       <c r="C35" t="n">
         <v>29.53244209289551</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>13.63507270812988</v>
+        <v>13.63506984710693</v>
       </c>
       <c r="C36" t="n">
         <v>25.49618339538574</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>15.73710250854492</v>
+        <v>15.73709869384766</v>
       </c>
       <c r="C37" t="n">
         <v>29.00763320922852</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>12.52756023406982</v>
+        <v>12.52755641937256</v>
       </c>
       <c r="C39" t="n">
         <v>23.09160232543945</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.07973289489746</v>
+        <v>14.07972812652588</v>
       </c>
       <c r="C40" t="n">
         <v>25.52480888366699</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>12.75860214233398</v>
+        <v>12.75860023498535</v>
       </c>
       <c r="C41" t="n">
         <v>23.12977027893066</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.51659679412842</v>
+        <v>14.51659774780273</v>
       </c>
       <c r="C42" t="n">
         <v>26.31679344177246</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.01620864868164</v>
+        <v>16.01620674133301</v>
       </c>
       <c r="C44" t="n">
         <v>28.63549613952637</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>17.30775260925293</v>
+        <v>17.3077507019043</v>
       </c>
       <c r="C45" t="n">
         <v>30.94465637207031</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>17.08502197265625</v>
+        <v>17.08502006530762</v>
       </c>
       <c r="C46" t="n">
         <v>30.18129730224609</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>16.70690727233887</v>
+        <v>16.70691299438477</v>
       </c>
       <c r="C47" t="n">
         <v>29.51335906982422</v>
@@ -1362,7 +1374,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1387,11 +1399,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.93899345397949</v>
+        <v>19.93899917602539</v>
       </c>
       <c r="C49" t="n">
         <v>34.86641311645508</v>
@@ -1412,11 +1424,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>20.83390808105469</v>
+        <v>20.83390426635742</v>
       </c>
       <c r="C50" t="n">
         <v>36.43129730224609</v>
@@ -1437,11 +1449,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>20.12453269958496</v>
+        <v>20.12452697753906</v>
       </c>
       <c r="C51" t="n">
         <v>35.19084167480469</v>
@@ -1462,11 +1474,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>20.59440231323242</v>
+        <v>20.59441184997559</v>
       </c>
       <c r="C52" t="n">
         <v>35.63931274414062</v>
@@ -1487,7 +1499,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1512,7 +1524,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1537,11 +1549,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>19.49591445922852</v>
+        <v>19.49590682983398</v>
       </c>
       <c r="C55" t="n">
         <v>33.36832046508789</v>
@@ -1562,11 +1574,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>19.21157836914062</v>
+        <v>19.21158409118652</v>
       </c>
       <c r="C56" t="n">
         <v>32.88167953491211</v>
@@ -1587,11 +1599,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>19.60183334350586</v>
+        <v>19.60183143615723</v>
       </c>
       <c r="C57" t="n">
         <v>33.54961776733398</v>
@@ -1612,11 +1624,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>20.73672294616699</v>
+        <v>20.73671913146973</v>
       </c>
       <c r="C58" t="n">
         <v>35.12404632568359</v>
@@ -1637,11 +1649,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>20.45503997802734</v>
+        <v>20.45505142211914</v>
       </c>
       <c r="C59" t="n">
         <v>34.64694595336914</v>
@@ -1662,11 +1674,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>19.41849708557129</v>
+        <v>19.41848945617676</v>
       </c>
       <c r="C60" t="n">
         <v>32.89122009277344</v>
@@ -1687,11 +1699,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.51959991455078</v>
+        <v>20.51959800720215</v>
       </c>
       <c r="C61" t="n">
         <v>34.38931274414062</v>
@@ -1712,11 +1724,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>18.88554954528809</v>
+        <v>18.88554191589355</v>
       </c>
       <c r="C62" t="n">
         <v>31.6507625579834</v>
@@ -1737,11 +1749,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>18.5439395904541</v>
+        <v>18.54393196105957</v>
       </c>
       <c r="C63" t="n">
         <v>31.07824325561523</v>
@@ -1766,11 +1778,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.01406860351562</v>
+        <v>19.01406288146973</v>
       </c>
       <c r="C64" t="n">
         <v>31.49809265136719</v>
@@ -1795,7 +1807,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1824,11 +1836,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>21.16833877563477</v>
+        <v>21.16833686828613</v>
       </c>
       <c r="C66" t="n">
         <v>35.06679534912109</v>
@@ -1853,11 +1865,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>20.5476188659668</v>
+        <v>20.54762649536133</v>
       </c>
       <c r="C67" t="n">
         <v>33.67366409301758</v>
@@ -1882,11 +1894,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>19.8722095489502</v>
+        <v>19.87221336364746</v>
       </c>
       <c r="C68" t="n">
         <v>32.56679534912109</v>
@@ -1911,11 +1923,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>19.27249336242676</v>
+        <v>19.27249717712402</v>
       </c>
       <c r="C69" t="n">
         <v>31.58396911621094</v>
@@ -1940,11 +1952,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>19.26840019226074</v>
+        <v>19.26840972900391</v>
       </c>
       <c r="C70" t="n">
         <v>31.20228958129883</v>
@@ -1969,11 +1981,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>20.32905960083008</v>
+        <v>20.32905197143555</v>
       </c>
       <c r="C71" t="n">
         <v>32.91984558105469</v>
@@ -1998,11 +2010,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>21.06561851501465</v>
+        <v>21.06560707092285</v>
       </c>
       <c r="C72" t="n">
         <v>34.11259460449219</v>
@@ -2027,11 +2039,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>22.48129463195801</v>
+        <v>22.48129081726074</v>
       </c>
       <c r="C73" t="n">
         <v>35.97328186035156</v>
@@ -2056,11 +2068,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>22.82120132446289</v>
+        <v>22.82120513916016</v>
       </c>
       <c r="C74" t="n">
         <v>36.51717758178711</v>
@@ -2085,7 +2097,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2114,11 +2126,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>23.15395927429199</v>
+        <v>23.15397071838379</v>
       </c>
       <c r="C76" t="n">
         <v>36.64122009277344</v>
@@ -2143,11 +2155,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>23.66045570373535</v>
+        <v>23.66045761108398</v>
       </c>
       <c r="C77" t="n">
         <v>37.4427490234375</v>
@@ -2172,11 +2184,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>22.6595344543457</v>
+        <v>22.65952491760254</v>
       </c>
       <c r="C78" t="n">
         <v>35.85877990722656</v>
@@ -2201,11 +2213,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>25.44902992248535</v>
+        <v>25.44902801513672</v>
       </c>
       <c r="C79" t="n">
         <v>39.83778762817383</v>
@@ -2230,11 +2242,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>26.92416000366211</v>
+        <v>26.92414855957031</v>
       </c>
       <c r="C80" t="n">
         <v>42.14694595336914</v>
@@ -2259,11 +2271,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>26.24145126342773</v>
+        <v>26.24145698547363</v>
       </c>
       <c r="C81" t="n">
         <v>41.07824325561523</v>
@@ -2288,11 +2300,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>27.7528076171875</v>
+        <v>27.7528133392334</v>
       </c>
       <c r="C82" t="n">
         <v>43.03435134887695</v>
@@ -2317,11 +2329,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>28.07894706726074</v>
+        <v>28.07895088195801</v>
       </c>
       <c r="C83" t="n">
         <v>43.54007720947266</v>
@@ -2346,11 +2358,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>27.26050758361816</v>
+        <v>27.26051139831543</v>
       </c>
       <c r="C84" t="n">
         <v>42.27099227905273</v>
@@ -2375,11 +2387,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>25.43454933166504</v>
+        <v>25.43454551696777</v>
       </c>
       <c r="C85" t="n">
         <v>39.06488418579102</v>
@@ -2404,11 +2416,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>26.86967658996582</v>
+        <v>26.86966896057129</v>
       </c>
       <c r="C86" t="n">
         <v>41.26908493041992</v>
@@ -2433,11 +2445,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>26.5466136932373</v>
+        <v>26.54660987854004</v>
       </c>
       <c r="C87" t="n">
         <v>40.77289962768555</v>
@@ -2462,11 +2474,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>27.72455215454102</v>
+        <v>27.72455787658691</v>
       </c>
       <c r="C88" t="n">
         <v>42.17557144165039</v>
@@ -2491,11 +2503,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>29.48087501525879</v>
+        <v>29.48085784912109</v>
       </c>
       <c r="C89" t="n">
         <v>44.84732818603516</v>
@@ -2520,11 +2532,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>29.29269027709961</v>
+        <v>29.29268074035645</v>
       </c>
       <c r="C90" t="n">
         <v>44.56106948852539</v>
@@ -2549,11 +2561,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>29.40345573425293</v>
+        <v>29.4034595489502</v>
       </c>
       <c r="C91" t="n">
         <v>44.32251739501953</v>
@@ -2578,7 +2590,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2607,11 +2619,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>29.9351978302002</v>
+        <v>29.93519020080566</v>
       </c>
       <c r="C93" t="n">
         <v>45.12404632568359</v>
@@ -2636,11 +2648,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>30.40938186645508</v>
+        <v>30.40937995910645</v>
       </c>
       <c r="C94" t="n">
         <v>45.42938995361328</v>
@@ -2665,11 +2677,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>28.79980659484863</v>
+        <v>28.79981231689453</v>
       </c>
       <c r="C95" t="n">
         <v>43.02481079101562</v>
@@ -2694,11 +2706,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>31.82733345031738</v>
+        <v>31.82734680175781</v>
       </c>
       <c r="C96" t="n">
         <v>47.54771041870117</v>
@@ -2723,11 +2735,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>32.25782012939453</v>
+        <v>32.2578125</v>
       </c>
       <c r="C97" t="n">
         <v>47.75763320922852</v>
@@ -2752,11 +2764,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>34.1397819519043</v>
+        <v>34.1397705078125</v>
       </c>
       <c r="C98" t="n">
         <v>50.54389190673828</v>
@@ -2781,11 +2793,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>36.73073577880859</v>
+        <v>36.73073196411133</v>
       </c>
       <c r="C99" t="n">
         <v>54.3797721862793</v>
@@ -2810,7 +2822,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2839,11 +2851,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>38.03720092773438</v>
+        <v>38.03720855712891</v>
       </c>
       <c r="C101" t="n">
         <v>55.87786483764648</v>
@@ -2868,11 +2880,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>37.58253479003906</v>
+        <v>37.58252334594727</v>
       </c>
       <c r="C102" t="n">
         <v>55.20992279052734</v>
@@ -2897,11 +2909,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>37.85927963256836</v>
+        <v>37.85928344726562</v>
       </c>
       <c r="C103" t="n">
         <v>55.20038223266602</v>
@@ -2926,11 +2938,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>37.13285064697266</v>
+        <v>37.13285827636719</v>
       </c>
       <c r="C104" t="n">
         <v>54.14122009277344</v>
@@ -2955,11 +2967,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>39.33832550048828</v>
+        <v>39.33832168579102</v>
       </c>
       <c r="C105" t="n">
         <v>57.35686874389648</v>
@@ -2984,11 +2996,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>39.078125</v>
+        <v>39.07812881469727</v>
       </c>
       <c r="C106" t="n">
         <v>56.56488418579102</v>
@@ -3013,11 +3025,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>38.19477844238281</v>
+        <v>38.19476699829102</v>
       </c>
       <c r="C107" t="n">
         <v>55.28625869750977</v>
@@ -3042,11 +3054,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.81644821166992</v>
+        <v>39.81644439697266</v>
       </c>
       <c r="C108" t="n">
         <v>57.63358688354492</v>
@@ -3071,11 +3083,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>37.71967315673828</v>
+        <v>37.71966171264648</v>
       </c>
       <c r="C109" t="n">
         <v>54.18893051147461</v>
@@ -3100,7 +3112,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3129,11 +3141,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>38.88201522827148</v>
+        <v>38.88201141357422</v>
       </c>
       <c r="C111" t="n">
         <v>55.85877990722656</v>
@@ -3158,11 +3170,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>38.48691177368164</v>
+        <v>38.48691940307617</v>
       </c>
       <c r="C112" t="n">
         <v>54.84732818603516</v>
@@ -3187,11 +3199,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>39.87961959838867</v>
+        <v>39.87960815429688</v>
       </c>
       <c r="C113" t="n">
         <v>56.83206176757812</v>
@@ -3216,11 +3228,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>40.77014923095703</v>
+        <v>40.77013778686523</v>
       </c>
       <c r="C114" t="n">
         <v>58.10114669799805</v>
@@ -3245,7 +3257,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3274,11 +3286,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>39.77816009521484</v>
+        <v>39.77815628051758</v>
       </c>
       <c r="C116" t="n">
         <v>56.25954055786133</v>
@@ -3303,11 +3315,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>36.33061981201172</v>
+        <v>36.33062744140625</v>
       </c>
       <c r="C117" t="n">
         <v>51.38358688354492</v>
@@ -3332,11 +3344,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>33.60850524902344</v>
+        <v>33.6085090637207</v>
       </c>
       <c r="C118" t="n">
         <v>47.12786483764648</v>
@@ -3361,11 +3373,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>37.19458389282227</v>
+        <v>37.194580078125</v>
       </c>
       <c r="C119" t="n">
         <v>52.15649032592773</v>
@@ -3390,11 +3402,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>36.07181167602539</v>
+        <v>36.07180786132812</v>
       </c>
       <c r="C120" t="n">
         <v>50.58206176757812</v>
@@ -3419,11 +3431,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>36.25312423706055</v>
+        <v>36.25312042236328</v>
       </c>
       <c r="C121" t="n">
         <v>50.40076446533203</v>
@@ -3448,11 +3460,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>34.7774543762207</v>
+        <v>34.77745819091797</v>
       </c>
       <c r="C122" t="n">
         <v>48.34923553466797</v>
@@ -3477,11 +3489,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>34.46174621582031</v>
+        <v>34.46173858642578</v>
       </c>
       <c r="C123" t="n">
         <v>47.91030502319336</v>
@@ -3506,11 +3518,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>36.63259506225586</v>
+        <v>36.63259887695312</v>
       </c>
       <c r="C124" t="n">
         <v>50.48664093017578</v>
@@ -3535,11 +3547,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>37.96884918212891</v>
+        <v>37.96885681152344</v>
       </c>
       <c r="C125" t="n">
         <v>52.32824325561523</v>
@@ -3564,11 +3576,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>38.95199203491211</v>
+        <v>38.95199584960938</v>
       </c>
       <c r="C126" t="n">
         <v>53.68320465087891</v>
@@ -3593,11 +3605,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>40.21228790283203</v>
+        <v>40.21227645874023</v>
       </c>
       <c r="C127" t="n">
         <v>54.97137451171875</v>
@@ -3622,7 +3634,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3651,11 +3663,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>43.82796859741211</v>
+        <v>43.82798385620117</v>
       </c>
       <c r="C129" t="n">
         <v>59.91412353515625</v>
@@ -3680,11 +3692,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>43.88216781616211</v>
+        <v>43.88217926025391</v>
       </c>
       <c r="C130" t="n">
         <v>59.5515251159668</v>
@@ -3709,11 +3721,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>41.28763580322266</v>
+        <v>41.28762817382812</v>
       </c>
       <c r="C131" t="n">
         <v>56.03053283691406</v>
@@ -3738,11 +3750,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>43.02437591552734</v>
+        <v>43.02436065673828</v>
       </c>
       <c r="C132" t="n">
         <v>58.38740539550781</v>
@@ -3767,7 +3779,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3796,11 +3808,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>43.92131805419922</v>
+        <v>43.92132568359375</v>
       </c>
       <c r="C134" t="n">
         <v>59.15076446533203</v>
@@ -3825,11 +3837,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>46.67039108276367</v>
+        <v>46.67038726806641</v>
       </c>
       <c r="C135" t="n">
         <v>62.85305404663086</v>
@@ -3854,11 +3866,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>45.34441757202148</v>
+        <v>45.34440612792969</v>
       </c>
       <c r="C136" t="n">
         <v>60.6297721862793</v>
@@ -3883,11 +3895,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>44.48091125488281</v>
+        <v>44.48091888427734</v>
       </c>
       <c r="C137" t="n">
         <v>59.47518920898438</v>
@@ -3912,11 +3924,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>46.46481323242188</v>
+        <v>46.46480941772461</v>
       </c>
       <c r="C138" t="n">
         <v>62.12786483764648</v>
@@ -3941,11 +3953,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>46.07319641113281</v>
+        <v>46.07320022583008</v>
       </c>
       <c r="C139" t="n">
         <v>61.15457916259766</v>
@@ -3970,11 +3982,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>45.92224884033203</v>
+        <v>45.92224502563477</v>
       </c>
       <c r="C140" t="n">
         <v>60.95419692993164</v>
@@ -3999,11 +4011,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>45.90786361694336</v>
+        <v>45.90785980224609</v>
       </c>
       <c r="C141" t="n">
         <v>60.93511581420898</v>
@@ -4028,11 +4040,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>46.36300659179688</v>
+        <v>46.36300277709961</v>
       </c>
       <c r="C142" t="n">
         <v>61.09732818603516</v>
@@ -4057,7 +4069,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4086,11 +4098,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>40.02004623413086</v>
+        <v>40.02006149291992</v>
       </c>
       <c r="C144" t="n">
         <v>52.73854827880859</v>
@@ -4115,11 +4127,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>41.0906982421875</v>
+        <v>41.09070205688477</v>
       </c>
       <c r="C145" t="n">
         <v>53.6927490234375</v>
@@ -4144,11 +4156,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>43.26683044433594</v>
+        <v>43.26682281494141</v>
       </c>
       <c r="C146" t="n">
         <v>56.53625869750977</v>
@@ -4173,11 +4185,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>39.59370803833008</v>
+        <v>39.59370422363281</v>
       </c>
       <c r="C147" t="n">
         <v>51.73664093017578</v>
@@ -4202,11 +4214,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>40.12409210205078</v>
+        <v>40.12409973144531</v>
       </c>
       <c r="C148" t="n">
         <v>51.97518920898438</v>
@@ -4231,11 +4243,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>43.36526489257812</v>
+        <v>43.36525726318359</v>
       </c>
       <c r="C149" t="n">
         <v>56.17366409301758</v>
@@ -4260,11 +4272,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>43.8514404296875</v>
+        <v>43.85142517089844</v>
       </c>
       <c r="C150" t="n">
         <v>56.80343627929688</v>
@@ -4289,11 +4301,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>45.0588493347168</v>
+        <v>45.05884552001953</v>
       </c>
       <c r="C151" t="n">
         <v>57.91984558105469</v>
@@ -4318,11 +4330,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>48.89664459228516</v>
+        <v>48.89663696289062</v>
       </c>
       <c r="C152" t="n">
         <v>62.85305404663086</v>
@@ -4347,11 +4359,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>50.91575241088867</v>
+        <v>50.91574859619141</v>
       </c>
       <c r="C153" t="n">
         <v>65.44847106933594</v>
@@ -4376,11 +4388,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>53.01950836181641</v>
+        <v>53.0195198059082</v>
       </c>
       <c r="C154" t="n">
         <v>67.69084167480469</v>
@@ -4405,11 +4417,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>55.01502990722656</v>
+        <v>55.01503372192383</v>
       </c>
       <c r="C155" t="n">
         <v>70.23854827880859</v>
@@ -4434,11 +4446,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>59.29755401611328</v>
+        <v>59.29754638671875</v>
       </c>
       <c r="C156" t="n">
         <v>75.70610809326172</v>
@@ -4463,11 +4475,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>57.50804138183594</v>
+        <v>57.50802230834961</v>
       </c>
       <c r="C157" t="n">
         <v>72.91030120849609</v>
@@ -4492,11 +4504,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>56.01782989501953</v>
+        <v>56.0178108215332</v>
       </c>
       <c r="C158" t="n">
         <v>71.02098846435547</v>
@@ -4521,11 +4533,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>61.18084335327148</v>
+        <v>61.18083953857422</v>
       </c>
       <c r="C159" t="n">
         <v>77.56679534912109</v>
@@ -4550,11 +4562,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>63.02053070068359</v>
+        <v>63.02053833007812</v>
       </c>
       <c r="C160" t="n">
         <v>79.36068725585938</v>
@@ -4579,11 +4591,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>59.64104843139648</v>
+        <v>59.64105606079102</v>
       </c>
       <c r="C161" t="n">
         <v>75.10496520996094</v>
@@ -4608,11 +4620,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>60.01992797851562</v>
+        <v>60.01993179321289</v>
       </c>
       <c r="C162" t="n">
         <v>75.58206176757812</v>
@@ -4637,11 +4649,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>63.96015167236328</v>
+        <v>63.96014404296875</v>
       </c>
       <c r="C163" t="n">
         <v>80.00954437255859</v>
@@ -4666,7 +4678,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4695,11 +4707,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>65.95865631103516</v>
+        <v>65.95867919921875</v>
       </c>
       <c r="C165" t="n">
         <v>82.50954437255859</v>
@@ -4724,11 +4736,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>64.63859558105469</v>
+        <v>64.63860321044922</v>
       </c>
       <c r="C166" t="n">
         <v>80.32442474365234</v>
@@ -4753,11 +4765,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>66.54290008544922</v>
+        <v>66.54291534423828</v>
       </c>
       <c r="C167" t="n">
         <v>82.69084167480469</v>
@@ -4782,11 +4794,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>66.94217681884766</v>
+        <v>66.94218444824219</v>
       </c>
       <c r="C168" t="n">
         <v>83.18701934814453</v>
@@ -4811,11 +4823,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>70.31589508056641</v>
+        <v>70.31588745117188</v>
       </c>
       <c r="C169" t="n">
         <v>86.78434753417969</v>
@@ -4840,11 +4852,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>66.05596160888672</v>
+        <v>66.05598449707031</v>
       </c>
       <c r="C170" t="n">
         <v>81.52671813964844</v>
@@ -4869,11 +4881,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>59.19060134887695</v>
+        <v>59.19058990478516</v>
       </c>
       <c r="C171" t="n">
         <v>73.05343627929688</v>
@@ -4898,11 +4910,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>59.97580337524414</v>
+        <v>59.97578430175781</v>
       </c>
       <c r="C172" t="n">
         <v>73.41603088378906</v>
@@ -4927,11 +4939,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>61.84663391113281</v>
+        <v>61.84662628173828</v>
       </c>
       <c r="C173" t="n">
         <v>75.70610809326172</v>
@@ -4956,11 +4968,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>62.9223747253418</v>
+        <v>62.92234802246094</v>
       </c>
       <c r="C174" t="n">
         <v>77.02290344238281</v>
@@ -4985,7 +4997,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5014,11 +5026,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>63.04539489746094</v>
+        <v>63.04537963867188</v>
       </c>
       <c r="C176" t="n">
         <v>76.56488800048828</v>
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>66.99751281738281</v>
+        <v>66.99750518798828</v>
       </c>
       <c r="C177" t="n">
         <v>81.364501953125</v>
@@ -5072,11 +5084,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>65.64868927001953</v>
+        <v>65.64866638183594</v>
       </c>
       <c r="C178" t="n">
         <v>79.15076446533203</v>
@@ -5101,11 +5113,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>59.52305603027344</v>
+        <v>59.52305221557617</v>
       </c>
       <c r="C179" t="n">
         <v>71.76526641845703</v>
@@ -5130,11 +5142,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>63.62262344360352</v>
+        <v>63.62262725830078</v>
       </c>
       <c r="C180" t="n">
         <v>76.70801544189453</v>
@@ -5159,11 +5171,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>65.24979400634766</v>
+        <v>65.24978637695312</v>
       </c>
       <c r="C181" t="n">
         <v>78.05343627929688</v>
@@ -5188,11 +5200,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>61.47677230834961</v>
+        <v>61.47679138183594</v>
       </c>
       <c r="C182" t="n">
         <v>73.54007720947266</v>
@@ -5217,11 +5229,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>57.9271240234375</v>
+        <v>57.92711639404297</v>
       </c>
       <c r="C183" t="n">
         <v>69.29389190673828</v>
@@ -5246,11 +5258,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>62.03301239013672</v>
+        <v>62.03301620483398</v>
       </c>
       <c r="C184" t="n">
         <v>73.55915832519531</v>
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>59.94887924194336</v>
+        <v>59.94888687133789</v>
       </c>
       <c r="C185" t="n">
         <v>71.08778381347656</v>
@@ -5304,11 +5316,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>61.06739807128906</v>
+        <v>61.06738662719727</v>
       </c>
       <c r="C186" t="n">
         <v>72.41412353515625</v>
@@ -5333,7 +5345,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5362,11 +5374,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>65.38227844238281</v>
+        <v>65.38230133056641</v>
       </c>
       <c r="C188" t="n">
         <v>76.87000274658203</v>
@@ -5391,11 +5403,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>64.88896942138672</v>
+        <v>64.88896179199219</v>
       </c>
       <c r="C189" t="n">
         <v>76.29000091552734</v>
@@ -5420,11 +5432,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>64.45782470703125</v>
+        <v>64.45784759521484</v>
       </c>
       <c r="C190" t="n">
         <v>75.11000061035156</v>
@@ -5449,11 +5461,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>75.56268310546875</v>
+        <v>75.56267547607422</v>
       </c>
       <c r="C191" t="n">
         <v>88.05000305175781</v>
@@ -5478,11 +5490,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>64.28619384765625</v>
+        <v>64.28620147705078</v>
       </c>
       <c r="C192" t="n">
         <v>74.91000366210938</v>
@@ -5507,11 +5519,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>66.39482879638672</v>
+        <v>66.39482116699219</v>
       </c>
       <c r="C193" t="n">
         <v>76.63999938964844</v>
@@ -5536,11 +5548,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>70.58782196044922</v>
+        <v>70.58779907226562</v>
       </c>
       <c r="C194" t="n">
         <v>81.48000335693359</v>
@@ -5565,11 +5577,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>66.34285736083984</v>
+        <v>66.34284973144531</v>
       </c>
       <c r="C195" t="n">
         <v>76.58000183105469</v>
@@ -5594,11 +5606,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>71.71390533447266</v>
+        <v>71.71389770507812</v>
       </c>
       <c r="C196" t="n">
         <v>82.05000305175781</v>
@@ -5623,11 +5635,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>77.5174560546875</v>
+        <v>77.51744842529297</v>
       </c>
       <c r="C197" t="n">
         <v>88.69000244140625</v>
@@ -5652,11 +5664,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>80.43668365478516</v>
+        <v>80.43669128417969</v>
       </c>
       <c r="C198" t="n">
         <v>92.02999877929688</v>
@@ -5681,7 +5693,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5710,11 +5722,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>78.72463226318359</v>
+        <v>78.72461700439453</v>
       </c>
       <c r="C200" t="n">
         <v>89.33999633789062</v>
@@ -5739,7 +5751,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5768,7 +5780,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5797,11 +5809,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>89.89430999755859</v>
+        <v>89.89430236816406</v>
       </c>
       <c r="C203" t="n">
         <v>101.1999969482422</v>
@@ -5826,11 +5838,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>97.81781005859375</v>
+        <v>97.81780242919922</v>
       </c>
       <c r="C204" t="n">
         <v>110.120002746582</v>
@@ -5855,11 +5867,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>99.20806884765625</v>
+        <v>99.20807647705078</v>
       </c>
       <c r="C205" t="n">
         <v>110.9499969482422</v>
@@ -5884,11 +5896,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>96.04270935058594</v>
+        <v>96.042724609375</v>
       </c>
       <c r="C206" t="n">
         <v>107.4100036621094</v>
@@ -5913,11 +5925,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>94.99653625488281</v>
+        <v>94.99652099609375</v>
       </c>
       <c r="C207" t="n">
         <v>106.2399978637695</v>
@@ -5942,7 +5954,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5971,11 +5983,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>103.9675369262695</v>
+        <v>103.9675445556641</v>
       </c>
       <c r="C209" t="n">
         <v>115.4700012207031</v>
@@ -6000,11 +6012,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>99.41158294677734</v>
+        <v>99.41157531738281</v>
       </c>
       <c r="C210" t="n">
         <v>110.4100036621094</v>
@@ -6029,11 +6041,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>104.5896682739258</v>
+        <v>104.5896530151367</v>
       </c>
       <c r="C211" t="n">
         <v>115.3899993896484</v>
@@ -6058,11 +6070,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>96.66771697998047</v>
+        <v>96.66770172119141</v>
       </c>
       <c r="C212" t="n">
         <v>106.6500015258789</v>
@@ -6087,11 +6099,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>98.77962493896484</v>
+        <v>98.77964019775391</v>
       </c>
       <c r="C213" t="n">
         <v>108.9800033569336</v>
@@ -6116,11 +6128,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>93.95018005371094</v>
+        <v>93.95017242431641</v>
       </c>
       <c r="C214" t="n">
         <v>102.9499969482422</v>
@@ -6145,11 +6157,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>93.72205352783203</v>
+        <v>93.72203063964844</v>
       </c>
       <c r="C215" t="n">
         <v>102.6999969482422</v>
@@ -6174,11 +6186,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>93.52127838134766</v>
+        <v>93.52127075195312</v>
       </c>
       <c r="C216" t="n">
         <v>102.4800033569336</v>
@@ -6203,11 +6215,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>100.2099533081055</v>
+        <v>100.2099456787109</v>
       </c>
       <c r="C217" t="n">
         <v>109.0199966430664</v>
@@ -6232,7 +6244,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6261,7 +6273,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6290,11 +6302,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>122.0562744140625</v>
+        <v>122.056282043457</v>
       </c>
       <c r="C220" t="n">
         <v>131.9499969482422</v>
@@ -6319,7 +6331,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6348,11 +6360,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>116.1269073486328</v>
+        <v>116.1269149780273</v>
       </c>
       <c r="C222" t="n">
         <v>125.5400009155273</v>
@@ -6377,7 +6389,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6406,11 +6418,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>105.2734756469727</v>
+        <v>105.2734603881836</v>
       </c>
       <c r="C224" t="n">
         <v>113.129997253418</v>
@@ -6435,7 +6447,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6464,7 +6476,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6493,11 +6505,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>95.85120391845703</v>
+        <v>95.85121154785156</v>
       </c>
       <c r="C227" t="n">
         <v>102.3199996948242</v>
@@ -6522,7 +6534,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6551,11 +6563,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>93.93672943115234</v>
+        <v>93.93673706054688</v>
       </c>
       <c r="C229" t="n">
         <v>99.48000335693359</v>
@@ -6580,11 +6592,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>93.31352233886719</v>
+        <v>93.31351470947266</v>
       </c>
       <c r="C230" t="n">
         <v>98.81999969482422</v>
@@ -6609,7 +6621,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6638,11 +6650,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>85.49057769775391</v>
+        <v>85.49058532714844</v>
       </c>
       <c r="C232" t="n">
         <v>89.76000213623047</v>
@@ -6667,11 +6679,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>81.14747619628906</v>
+        <v>81.14746856689453</v>
       </c>
       <c r="C233" t="n">
         <v>85.19999694824219</v>
@@ -6696,11 +6708,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>73.18512725830078</v>
+        <v>73.18511962890625</v>
       </c>
       <c r="C234" t="n">
         <v>76.83999633789062</v>
@@ -6725,11 +6737,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>76.14965057373047</v>
+        <v>76.149658203125</v>
       </c>
       <c r="C235" t="n">
         <v>79.16000366210938</v>
@@ -6754,11 +6766,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>75.14920806884766</v>
+        <v>75.14920043945312</v>
       </c>
       <c r="C236" t="n">
         <v>78.12000274658203</v>
@@ -6783,11 +6795,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>80.92103576660156</v>
+        <v>80.92102813720703</v>
       </c>
       <c r="C237" t="n">
         <v>84.12000274658203</v>
@@ -6812,11 +6824,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>81.53578948974609</v>
+        <v>81.53579711914062</v>
       </c>
       <c r="C238" t="n">
         <v>83.93000030517578</v>
@@ -6841,7 +6853,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6870,11 +6882,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>101.8395919799805</v>
+        <v>101.839599609375</v>
       </c>
       <c r="C240" t="n">
         <v>104.8300018310547</v>
@@ -6899,7 +6911,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6928,7 +6940,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6957,7 +6969,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6986,7 +6998,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7015,7 +7027,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7044,7 +7056,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7102,7 +7114,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7131,7 +7143,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7160,32 +7172,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>148.0800018310547</v>
+        <v>147.9799957275391</v>
       </c>
       <c r="C250" t="n">
-        <v>148.0800018310547</v>
+        <v>147.9799957275391</v>
       </c>
       <c r="D250" t="n">
-        <v>159697500</v>
+        <v>170009800</v>
       </c>
       <c r="E250" t="n">
         <v>1.250000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>118.4640014648436</v>
+        <v>118.3839965820311</v>
       </c>
       <c r="G250" t="n">
         <v>2467171638</v>
       </c>
       <c r="H250" t="n">
-        <v>365338780672.5662</v>
+        <v>365092048450.3456</v>
       </c>
       <c r="I250" t="n">
-        <v>0.06472897853570413</v>
+        <v>0.06890878501579142</v>
       </c>
     </row>
   </sheetData>
@@ -7217,75 +7229,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7531,13 +7543,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7573,13 +7585,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7615,13 +7627,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7648,7 +7660,7 @@
       <c r="I10" t="n">
         <v>0.2671755725190841</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7661,13 +7673,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7694,7 +7706,7 @@
       <c r="I11" t="n">
         <v>0.5057251908396947</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="K11" t="n">
@@ -7707,13 +7719,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7740,7 +7752,7 @@
       <c r="I12" t="n">
         <v>0.8969465648854964</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="K12" t="n">
@@ -7753,13 +7765,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7786,7 +7798,7 @@
       <c r="I13" t="n">
         <v>1.316793893129771</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="K13" t="n">
@@ -7799,13 +7811,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7832,7 +7844,7 @@
       <c r="I14" t="n">
         <v>1.927480916030535</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K14" t="n">
@@ -7845,13 +7857,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7878,7 +7890,7 @@
       <c r="I15" t="n">
         <v>2.137404580152672</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K15" t="n">
@@ -7891,13 +7903,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7924,7 +7936,7 @@
       <c r="I16" t="n">
         <v>2.070610687022901</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K16" t="n">
@@ -7937,13 +7949,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7970,7 +7982,7 @@
       <c r="I17" t="n">
         <v>2.080152671755726</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="K17" t="n">
@@ -7983,13 +7995,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8016,7 +8028,7 @@
       <c r="I18" t="n">
         <v>1.908396946564885</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K18" t="n">
@@ -8029,13 +8041,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8062,7 +8074,7 @@
       <c r="I19" t="n">
         <v>1.870229007633588</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="K19" t="n">
@@ -8075,13 +8087,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8108,7 +8120,7 @@
       <c r="I20" t="n">
         <v>1.603053435114504</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K20" t="n">
@@ -8121,13 +8133,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8154,7 +8166,7 @@
       <c r="I21" t="n">
         <v>1.431297709923664</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="K21" t="n">
@@ -8167,13 +8179,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8200,7 +8212,7 @@
       <c r="I22" t="n">
         <v>1.402671755725191</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K22" t="n">
@@ -8213,13 +8225,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8246,7 +8258,7 @@
       <c r="I23" t="n">
         <v>1.450381679389313</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K23" t="n">
@@ -8259,13 +8271,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8292,7 +8304,7 @@
       <c r="I24" t="n">
         <v>1.812977099236641</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="K24" t="n">
@@ -8305,13 +8317,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8338,7 +8350,7 @@
       <c r="I25" t="n">
         <v>1.74618320610687</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="K25" t="n">
@@ -8351,13 +8363,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8384,7 +8396,7 @@
       <c r="I26" t="n">
         <v>3.883587786259542</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K26" t="n">
@@ -8397,13 +8409,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8430,7 +8442,7 @@
       <c r="I27" t="n">
         <v>3.654580152671756</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K27" t="n">
@@ -8443,13 +8455,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8476,7 +8488,7 @@
       <c r="I28" t="n">
         <v>3.234732824427482</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K28" t="n">
@@ -8489,13 +8501,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8522,7 +8534,7 @@
       <c r="I29" t="n">
         <v>3.549618320610688</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K29" t="n">
@@ -8535,13 +8547,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8568,7 +8580,7 @@
       <c r="I30" t="n">
         <v>1.488549618320611</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K30" t="n">
@@ -8581,13 +8593,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42499</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8614,7 +8626,7 @@
       <c r="I31" t="n">
         <v>1.555343511450382</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42499</v>
       </c>
       <c r="K31" t="n">
@@ -8627,13 +8639,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8660,7 +8672,7 @@
       <c r="I32" t="n">
         <v>1.736641221374046</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="K32" t="n">
@@ -8673,13 +8685,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8706,7 +8718,7 @@
       <c r="I33" t="n">
         <v>1.870229007633588</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="K33" t="n">
@@ -8719,13 +8731,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8752,7 +8764,7 @@
       <c r="I34" t="n">
         <v>1.345419847328245</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="K34" t="n">
@@ -8765,13 +8777,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8798,7 +8810,7 @@
       <c r="I35" t="n">
         <v>1.498091603053435</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="K35" t="n">
@@ -8811,13 +8823,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8844,7 +8856,7 @@
       <c r="I36" t="n">
         <v>1.765267175572519</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="K36" t="n">
@@ -8857,13 +8869,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8890,7 +8902,7 @@
       <c r="I37" t="n">
         <v>1.001908396946565</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="K37" t="n">
@@ -8903,13 +8915,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8936,7 +8948,7 @@
       <c r="I38" t="n">
         <v>0.8301526717557255</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K38" t="n">
@@ -8949,13 +8961,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8982,7 +8994,7 @@
       <c r="I39" t="n">
         <v>0.5534351145038171</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="K39" t="n">
@@ -8995,13 +9007,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9028,7 +9040,7 @@
       <c r="I40" t="n">
         <v>0.4770992366412218</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="K40" t="n">
@@ -9041,13 +9053,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9074,7 +9086,7 @@
       <c r="I41" t="n">
         <v>1.192748091603054</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="K41" t="n">
@@ -9087,13 +9099,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9120,7 +9132,7 @@
       <c r="I42" t="n">
         <v>2.213740458015268</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="K42" t="n">
@@ -9133,13 +9145,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9166,7 +9178,7 @@
       <c r="I43" t="n">
         <v>3.024809160305344</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="K43" t="n">
@@ -9179,13 +9191,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9212,7 +9224,7 @@
       <c r="I44" t="n">
         <v>3.406488549618321</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K44" t="n">
@@ -9225,13 +9237,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9258,7 +9270,7 @@
       <c r="I45" t="n">
         <v>3.416030534351145</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="K45" t="n">
@@ -9271,13 +9283,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9304,7 +9316,7 @@
       <c r="I46" t="n">
         <v>3.635496183206107</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="K46" t="n">
@@ -9317,13 +9329,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9350,7 +9362,7 @@
       <c r="I47" t="n">
         <v>3.769083969465649</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K47" t="n">
@@ -9363,13 +9375,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9396,7 +9408,7 @@
       <c r="I48" t="n">
         <v>3.912213740458015</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K48" t="n">
@@ -9409,13 +9421,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9442,7 +9454,7 @@
       <c r="I49" t="n">
         <v>4.312977099236641</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K49" t="n">
@@ -9455,13 +9467,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9488,7 +9500,7 @@
       <c r="I50" t="n">
         <v>2.652671755725191</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K50" t="n">
@@ -9501,13 +9513,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9534,7 +9546,7 @@
       <c r="I51" t="n">
         <v>2.643129770992367</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K51" t="n">
@@ -9547,13 +9559,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44417</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9580,7 +9592,7 @@
       <c r="I52" t="n">
         <v>2.127175572519084</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44417</v>
       </c>
       <c r="K52" t="n">
@@ -9593,13 +9605,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9626,7 +9638,7 @@
       <c r="I53" t="n">
         <v>2.820305343511451</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K53" t="n">
@@ -9639,13 +9651,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9672,7 +9684,7 @@
       <c r="I54" t="n">
         <v>5.140000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K54" t="n">
@@ -9685,13 +9697,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9718,7 +9730,7 @@
       <c r="I55" t="n">
         <v>5.647251908396947</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K55" t="n">
@@ -9731,13 +9743,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9764,7 +9776,7 @@
       <c r="I56" t="n">
         <v>6.587251908396947</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K56" t="n">
@@ -9777,13 +9789,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9810,7 +9822,7 @@
       <c r="I57" t="n">
         <v>6.067251908396947</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K57" t="n">
@@ -9823,13 +9835,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9856,7 +9868,7 @@
       <c r="I58" t="n">
         <v>5.71</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="K58" t="n">
@@ -9869,13 +9881,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9902,7 +9914,7 @@
       <c r="I59" t="n">
         <v>5.12</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="K59" t="n">
@@ -9915,13 +9927,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9948,7 +9960,7 @@
       <c r="I60" t="n">
         <v>1.22</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="K60" t="n">
@@ -9961,13 +9973,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9994,7 +10006,7 @@
       <c r="I61" t="n">
         <v>1.8</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K61" t="n">
@@ -10007,13 +10019,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10040,7 +10052,7 @@
       <c r="I62" t="n">
         <v>0.1400000000000005</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="K62" t="n">
@@ -10053,13 +10065,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10086,7 +10098,7 @@
       <c r="I63" t="n">
         <v>0.9000000000000005</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="K63" t="n">
@@ -10099,13 +10111,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10132,7 +10144,7 @@
       <c r="I64" t="n">
         <v>5.390000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="K64" t="n">
@@ -10145,13 +10157,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10178,7 +10190,7 @@
       <c r="I65" t="n">
         <v>4.77</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="K65" t="n">
@@ -10191,13 +10203,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10224,7 +10236,7 @@
       <c r="I66" t="n">
         <v>6.740000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="K66" t="n">
@@ -10237,13 +10249,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10270,7 +10282,7 @@
       <c r="I67" t="n">
         <v>6.880000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K67" t="n">
@@ -10283,13 +10295,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10316,7 +10328,7 @@
       <c r="I68" t="n">
         <v>6.5</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K68" t="n">
@@ -10329,13 +10341,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10362,7 +10374,7 @@
       <c r="I69" t="n">
         <v>7.580000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K69" t="n">
@@ -10375,13 +10387,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10408,7 +10420,7 @@
       <c r="I70" t="n">
         <v>7.280000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="K70" t="n">
@@ -10421,13 +10433,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10454,7 +10466,7 @@
       <c r="I71" t="n">
         <v>3.550000000000002</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="K71" t="n">
@@ -10467,13 +10479,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10500,7 +10512,7 @@
       <c r="I72" t="n">
         <v>1.250000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="K72" t="n">
@@ -10537,52 +10549,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="C2" t="n">
@@ -10611,10 +10623,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40207</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="C3" t="n">
@@ -10643,10 +10655,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C4" t="n">
@@ -10675,10 +10687,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C5" t="n">
@@ -10707,10 +10719,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C6" t="n">
@@ -10739,10 +10751,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C7" t="n">
@@ -10771,10 +10783,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="C8" t="n">
@@ -10803,10 +10815,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="C9" t="n">
@@ -10835,10 +10847,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="C10" t="n">
@@ -10867,10 +10879,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C11" t="n">
@@ -10899,10 +10911,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C12" t="n">
@@ -10931,10 +10943,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C13" t="n">
@@ -10963,10 +10975,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="C14" t="n">
@@ -10995,10 +11007,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C15" t="n">
@@ -11027,10 +11039,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="C16" t="n">
@@ -11059,10 +11071,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C17" t="n">
@@ -11091,10 +11103,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C18" t="n">
@@ -11123,10 +11135,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C19" t="n">
@@ -11155,10 +11167,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C20" t="n">
@@ -11187,10 +11199,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="C21" t="n">
@@ -11219,10 +11231,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="C22" t="n">
@@ -11251,10 +11263,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C23" t="n">
@@ -11283,10 +11295,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C24" t="n">
@@ -11315,10 +11327,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C25" t="n">
@@ -11347,10 +11359,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C26" t="n">
@@ -11379,10 +11391,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C27" t="n">
@@ -11411,10 +11423,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42499</v>
       </c>
       <c r="C28" t="n">
@@ -11443,10 +11455,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="C29" t="n">
@@ -11475,10 +11487,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="C30" t="n">
@@ -11507,10 +11519,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="C31" t="n">
@@ -11539,10 +11551,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="C32" t="n">
@@ -11571,10 +11583,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="C33" t="n">
@@ -11603,10 +11615,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="C34" t="n">
@@ -11635,10 +11647,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C35" t="n">
@@ -11667,10 +11679,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="C36" t="n">
@@ -11699,10 +11711,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="C37" t="n">
@@ -11731,10 +11743,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="C38" t="n">
@@ -11763,10 +11775,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="C39" t="n">
@@ -11795,10 +11807,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="C40" t="n">
@@ -11827,10 +11839,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C41" t="n">
@@ -11859,10 +11871,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C42" t="n">
@@ -11891,10 +11903,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="C43" t="n">
@@ -11923,10 +11935,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C44" t="n">
@@ -11955,10 +11967,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C45" t="n">
@@ -11987,10 +11999,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C46" t="n">
@@ -12019,10 +12031,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C47" t="n">
@@ -12051,10 +12063,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C48" t="n">
@@ -12083,10 +12095,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44417</v>
       </c>
       <c r="C49" t="n">
@@ -12115,10 +12127,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C50" t="n">
@@ -12147,10 +12159,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="C51" t="n">
@@ -12179,10 +12191,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C52" t="n">
@@ -12211,10 +12223,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C53" t="n">
@@ -12243,10 +12255,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C54" t="n">
@@ -12275,10 +12287,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="C55" t="n">
@@ -12307,10 +12319,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="C56" t="n">
@@ -12339,10 +12351,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="C57" t="n">
@@ -12371,10 +12383,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C58" t="n">
@@ -12403,10 +12415,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="C59" t="n">
@@ -12435,10 +12447,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="C60" t="n">
@@ -12467,10 +12479,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="C61" t="n">
@@ -12499,10 +12511,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="C62" t="n">
@@ -12531,10 +12543,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="C63" t="n">
@@ -12563,10 +12575,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C64" t="n">
@@ -12595,10 +12607,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C65" t="n">
@@ -12627,10 +12639,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C66" t="n">
@@ -12659,10 +12671,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="C67" t="n">
@@ -12691,10 +12703,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="C68" t="n">
@@ -12723,10 +12735,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="C69" t="n">
@@ -12773,12 +12785,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MRK.xlsx
+++ b/salidas/empresas/MRK.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>15.93143653869629</v>
+        <v>15.93143558502197</v>
       </c>
       <c r="C2" t="n">
         <v>32.91984558105469</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>16.09768104553223</v>
+        <v>16.09768676757812</v>
       </c>
       <c r="C3" t="n">
         <v>33.26335906982422</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>16.44762420654297</v>
+        <v>16.4476203918457</v>
       </c>
       <c r="C4" t="n">
         <v>33.61641311645508</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>16.06946182250977</v>
+        <v>16.06945610046387</v>
       </c>
       <c r="C5" t="n">
         <v>32.84350967407227</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>15.72218894958496</v>
+        <v>15.72218036651611</v>
       </c>
       <c r="C6" t="n">
         <v>31.76526641845703</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>17.20513916015625</v>
+        <v>17.20514678955078</v>
       </c>
       <c r="C7" t="n">
         <v>34.76145172119141</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>19.01869964599609</v>
+        <v>19.01869773864746</v>
       </c>
       <c r="C8" t="n">
         <v>38.42557144165039</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>19.32891464233398</v>
+        <v>19.32890701293945</v>
       </c>
       <c r="C9" t="n">
         <v>38.6927490234375</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>19.97240447998047</v>
+        <v>19.97241020202637</v>
       </c>
       <c r="C10" t="n">
         <v>39.98091506958008</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>21.65027809143066</v>
+        <v>21.6502799987793</v>
       </c>
       <c r="C11" t="n">
         <v>43.33969497680664</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>21.21651077270508</v>
+        <v>21.21651840209961</v>
       </c>
       <c r="C12" t="n">
         <v>42.47137451171875</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.95820426940918</v>
+        <v>20.95820999145508</v>
       </c>
       <c r="C13" t="n">
         <v>41.60305404663086</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>21.51100540161133</v>
+        <v>21.51099967956543</v>
       </c>
       <c r="C14" t="n">
         <v>42.70038223266602</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>21.22259140014648</v>
+        <v>21.22259330749512</v>
       </c>
       <c r="C15" t="n">
         <v>42.12786483764648</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>21.41436958312988</v>
+        <v>21.41437530517578</v>
       </c>
       <c r="C16" t="n">
         <v>42.14694595336914</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>24.93898773193359</v>
+        <v>24.93899536132812</v>
       </c>
       <c r="C17" t="n">
         <v>49.08396911621094</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>25.42867469787598</v>
+        <v>25.42865562438965</v>
       </c>
       <c r="C18" t="n">
         <v>50.04771041870117</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>24.32358741760254</v>
+        <v>24.32357788085938</v>
       </c>
       <c r="C19" t="n">
         <v>47.51908493041992</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>24.50429916381836</v>
+        <v>24.50429153442383</v>
       </c>
       <c r="C21" t="n">
         <v>47.87213516235352</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>25.43988800048828</v>
+        <v>25.43988990783691</v>
       </c>
       <c r="C22" t="n">
         <v>49.32251739501953</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.67339706420898</v>
+        <v>28.67339515686035</v>
       </c>
       <c r="C23" t="n">
         <v>55.59160232543945</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>29.21476173400879</v>
+        <v>29.21476364135742</v>
       </c>
       <c r="C24" t="n">
         <v>56.64122009277344</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>28.78691673278809</v>
+        <v>28.78692054748535</v>
       </c>
       <c r="C25" t="n">
         <v>55.4484748840332</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>22.83732414245605</v>
+        <v>22.83732223510742</v>
       </c>
       <c r="C26" t="n">
         <v>43.98854827880859</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>21.94563293457031</v>
+        <v>21.94562721252441</v>
       </c>
       <c r="C27" t="n">
         <v>42.27099227905273</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>19.00958633422852</v>
+        <v>19.00957679748535</v>
       </c>
       <c r="C29" t="n">
         <v>36.29771041870117</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>19.46932792663574</v>
+        <v>19.46932029724121</v>
       </c>
       <c r="C30" t="n">
         <v>37.17557144165039</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>19.02317237854004</v>
+        <v>19.02317047119141</v>
       </c>
       <c r="C31" t="n">
         <v>35.96374130249023</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>18.00362014770508</v>
+        <v>18.00361633300781</v>
       </c>
       <c r="C33" t="n">
         <v>34.03625869750977</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>16.10489463806152</v>
+        <v>16.10489845275879</v>
       </c>
       <c r="C34" t="n">
         <v>30.11450386047363</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>15.79360771179199</v>
+        <v>15.79362201690674</v>
       </c>
       <c r="C35" t="n">
         <v>29.53244209289551</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>13.63506984710693</v>
+        <v>13.63506889343262</v>
       </c>
       <c r="C36" t="n">
         <v>25.49618339538574</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>15.73709869384766</v>
+        <v>15.73709678649902</v>
       </c>
       <c r="C37" t="n">
         <v>29.00763320922852</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>14.77941513061523</v>
+        <v>14.77941417694092</v>
       </c>
       <c r="C38" t="n">
         <v>27.24236679077148</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>12.52755641937256</v>
+        <v>12.52755451202393</v>
       </c>
       <c r="C39" t="n">
         <v>23.09160232543945</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.07972812652588</v>
+        <v>14.0797290802002</v>
       </c>
       <c r="C40" t="n">
         <v>25.52480888366699</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>12.75860023498535</v>
+        <v>12.75860214233398</v>
       </c>
       <c r="C41" t="n">
         <v>23.12977027893066</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.51659774780273</v>
+        <v>14.51659679412842</v>
       </c>
       <c r="C42" t="n">
         <v>26.31679344177246</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.9221305847168</v>
+        <v>14.92212963104248</v>
       </c>
       <c r="C43" t="n">
         <v>26.67938995361328</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>17.3077507019043</v>
+        <v>17.3077564239502</v>
       </c>
       <c r="C45" t="n">
         <v>30.94465637207031</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>17.08502006530762</v>
+        <v>17.08502197265625</v>
       </c>
       <c r="C46" t="n">
         <v>30.18129730224609</v>
@@ -1378,7 +1378,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>19.55891036987305</v>
+        <v>19.55891418457031</v>
       </c>
       <c r="C48" t="n">
         <v>34.5515251159668</v>
@@ -1428,7 +1428,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>20.83390426635742</v>
+        <v>20.83390808105469</v>
       </c>
       <c r="C50" t="n">
         <v>36.43129730224609</v>
@@ -1453,7 +1453,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>20.12452697753906</v>
+        <v>20.12453079223633</v>
       </c>
       <c r="C51" t="n">
         <v>35.19084167480469</v>
@@ -1478,7 +1478,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>20.59441184997559</v>
+        <v>20.59440612792969</v>
       </c>
       <c r="C52" t="n">
         <v>35.63931274414062</v>
@@ -1503,7 +1503,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>19.32069969177246</v>
+        <v>19.32069396972656</v>
       </c>
       <c r="C53" t="n">
         <v>33.43511581420898</v>
@@ -1528,7 +1528,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.57631874084473</v>
+        <v>18.57632255554199</v>
       </c>
       <c r="C54" t="n">
         <v>32.14694595336914</v>
@@ -1553,7 +1553,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>19.49590682983398</v>
+        <v>19.49590873718262</v>
       </c>
       <c r="C55" t="n">
         <v>33.36832046508789</v>
@@ -1578,7 +1578,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>19.21158409118652</v>
+        <v>19.21157455444336</v>
       </c>
       <c r="C56" t="n">
         <v>32.88167953491211</v>
@@ -1628,7 +1628,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>20.73671913146973</v>
+        <v>20.73672103881836</v>
       </c>
       <c r="C58" t="n">
         <v>35.12404632568359</v>
@@ -1653,7 +1653,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>20.45505142211914</v>
+        <v>20.45504188537598</v>
       </c>
       <c r="C59" t="n">
         <v>34.64694595336914</v>
@@ -1728,7 +1728,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>18.88554191589355</v>
+        <v>18.88554573059082</v>
       </c>
       <c r="C62" t="n">
         <v>31.6507625579834</v>
@@ -1753,7 +1753,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>18.54393196105957</v>
+        <v>18.54393768310547</v>
       </c>
       <c r="C63" t="n">
         <v>31.07824325561523</v>
@@ -1782,7 +1782,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.01406288146973</v>
+        <v>19.01406478881836</v>
       </c>
       <c r="C64" t="n">
         <v>31.49809265136719</v>
@@ -1811,7 +1811,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>20.7075366973877</v>
+        <v>20.70753860473633</v>
       </c>
       <c r="C65" t="n">
         <v>34.30343627929688</v>
@@ -1840,7 +1840,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>21.16833686828613</v>
+        <v>21.1683464050293</v>
       </c>
       <c r="C66" t="n">
         <v>35.06679534912109</v>
@@ -1869,7 +1869,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>20.54762649536133</v>
+        <v>20.54762840270996</v>
       </c>
       <c r="C67" t="n">
         <v>33.67366409301758</v>
@@ -1898,7 +1898,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>19.87221336364746</v>
+        <v>19.87221527099609</v>
       </c>
       <c r="C68" t="n">
         <v>32.56679534912109</v>
@@ -1927,7 +1927,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>19.27249717712402</v>
+        <v>19.27249526977539</v>
       </c>
       <c r="C69" t="n">
         <v>31.58396911621094</v>
@@ -1956,7 +1956,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>19.26840972900391</v>
+        <v>19.26840591430664</v>
       </c>
       <c r="C70" t="n">
         <v>31.20228958129883</v>
@@ -1985,7 +1985,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>20.32905197143555</v>
+        <v>20.32905769348145</v>
       </c>
       <c r="C71" t="n">
         <v>32.91984558105469</v>
@@ -2014,7 +2014,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>21.06560707092285</v>
+        <v>21.06561470031738</v>
       </c>
       <c r="C72" t="n">
         <v>34.11259460449219</v>
@@ -2043,7 +2043,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>22.48129081726074</v>
+        <v>22.48129463195801</v>
       </c>
       <c r="C73" t="n">
         <v>35.97328186035156</v>
@@ -2101,7 +2101,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>22.76156616210938</v>
+        <v>22.76157188415527</v>
       </c>
       <c r="C75" t="n">
         <v>36.42175674438477</v>
@@ -2130,7 +2130,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>23.15397071838379</v>
+        <v>23.15396308898926</v>
       </c>
       <c r="C76" t="n">
         <v>36.64122009277344</v>
@@ -2188,7 +2188,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>22.65952491760254</v>
+        <v>22.65953254699707</v>
       </c>
       <c r="C78" t="n">
         <v>35.85877990722656</v>
@@ -2217,7 +2217,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>25.44902801513672</v>
+        <v>25.44903945922852</v>
       </c>
       <c r="C79" t="n">
         <v>39.83778762817383</v>
@@ -2246,7 +2246,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>26.92414855957031</v>
+        <v>26.92415809631348</v>
       </c>
       <c r="C80" t="n">
         <v>42.14694595336914</v>
@@ -2275,7 +2275,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>26.24145698547363</v>
+        <v>26.24145317077637</v>
       </c>
       <c r="C81" t="n">
         <v>41.07824325561523</v>
@@ -2304,7 +2304,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>27.7528133392334</v>
+        <v>27.75280380249023</v>
       </c>
       <c r="C82" t="n">
         <v>43.03435134887695</v>
@@ -2333,7 +2333,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>28.07895088195801</v>
+        <v>28.07895851135254</v>
       </c>
       <c r="C83" t="n">
         <v>43.54007720947266</v>
@@ -2362,7 +2362,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>27.26051139831543</v>
+        <v>27.26052474975586</v>
       </c>
       <c r="C84" t="n">
         <v>42.27099227905273</v>
@@ -2420,7 +2420,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>26.86966896057129</v>
+        <v>26.86967849731445</v>
       </c>
       <c r="C86" t="n">
         <v>41.26908493041992</v>
@@ -2478,7 +2478,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>27.72455787658691</v>
+        <v>27.72455978393555</v>
       </c>
       <c r="C88" t="n">
         <v>42.17557144165039</v>
@@ -2507,7 +2507,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>29.48085784912109</v>
+        <v>29.48087501525879</v>
       </c>
       <c r="C89" t="n">
         <v>44.84732818603516</v>
@@ -2536,7 +2536,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>29.29268074035645</v>
+        <v>29.29268646240234</v>
       </c>
       <c r="C90" t="n">
         <v>44.56106948852539</v>
@@ -2565,7 +2565,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>29.4034595489502</v>
+        <v>29.40345573425293</v>
       </c>
       <c r="C91" t="n">
         <v>44.32251739501953</v>
@@ -2594,7 +2594,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>30.49224281311035</v>
+        <v>30.49223899841309</v>
       </c>
       <c r="C92" t="n">
         <v>45.96374130249023</v>
@@ -2623,7 +2623,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>29.93519020080566</v>
+        <v>29.93520164489746</v>
       </c>
       <c r="C93" t="n">
         <v>45.12404632568359</v>
@@ -2652,7 +2652,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>30.40937995910645</v>
+        <v>30.40938949584961</v>
       </c>
       <c r="C94" t="n">
         <v>45.42938995361328</v>
@@ -2710,7 +2710,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>31.82734680175781</v>
+        <v>31.82735061645508</v>
       </c>
       <c r="C96" t="n">
         <v>47.54771041870117</v>
@@ -2768,7 +2768,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>34.1397705078125</v>
+        <v>34.13979339599609</v>
       </c>
       <c r="C98" t="n">
         <v>50.54389190673828</v>
@@ -2797,7 +2797,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>36.73073196411133</v>
+        <v>36.73071670532227</v>
       </c>
       <c r="C99" t="n">
         <v>54.3797721862793</v>
@@ -2826,7 +2826,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>36.87452697753906</v>
+        <v>36.8745231628418</v>
       </c>
       <c r="C100" t="n">
         <v>54.16984558105469</v>
@@ -2855,7 +2855,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>38.03720855712891</v>
+        <v>38.03721237182617</v>
       </c>
       <c r="C101" t="n">
         <v>55.87786483764648</v>
@@ -2884,7 +2884,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>37.58252334594727</v>
+        <v>37.5825309753418</v>
       </c>
       <c r="C102" t="n">
         <v>55.20992279052734</v>
@@ -2942,7 +2942,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>37.13285827636719</v>
+        <v>37.13286972045898</v>
       </c>
       <c r="C104" t="n">
         <v>54.14122009277344</v>
@@ -3000,7 +3000,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>39.07812881469727</v>
+        <v>39.078125</v>
       </c>
       <c r="C106" t="n">
         <v>56.56488418579102</v>
@@ -3029,7 +3029,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>38.19476699829102</v>
+        <v>38.19475936889648</v>
       </c>
       <c r="C107" t="n">
         <v>55.28625869750977</v>
@@ -3058,7 +3058,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.81644439697266</v>
+        <v>39.81643295288086</v>
       </c>
       <c r="C108" t="n">
         <v>57.63358688354492</v>
@@ -3087,7 +3087,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>37.71966171264648</v>
+        <v>37.71967697143555</v>
       </c>
       <c r="C109" t="n">
         <v>54.18893051147461</v>
@@ -3116,7 +3116,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>40.03771591186523</v>
+        <v>40.03772354125977</v>
       </c>
       <c r="C110" t="n">
         <v>57.51908493041992</v>
@@ -3174,7 +3174,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>38.48691940307617</v>
+        <v>38.48691558837891</v>
       </c>
       <c r="C112" t="n">
         <v>54.84732818603516</v>
@@ -3203,7 +3203,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>39.87960815429688</v>
+        <v>39.87961959838867</v>
       </c>
       <c r="C113" t="n">
         <v>56.83206176757812</v>
@@ -3232,7 +3232,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>40.77013778686523</v>
+        <v>40.7701416015625</v>
       </c>
       <c r="C114" t="n">
         <v>58.10114669799805</v>
@@ -3290,7 +3290,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>39.77815628051758</v>
+        <v>39.77816009521484</v>
       </c>
       <c r="C116" t="n">
         <v>56.25954055786133</v>
@@ -3319,7 +3319,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>36.33062744140625</v>
+        <v>36.33063125610352</v>
       </c>
       <c r="C117" t="n">
         <v>51.38358688354492</v>
@@ -3348,7 +3348,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>33.6085090637207</v>
+        <v>33.60851287841797</v>
       </c>
       <c r="C118" t="n">
         <v>47.12786483764648</v>
@@ -3377,7 +3377,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>37.194580078125</v>
+        <v>37.1945915222168</v>
       </c>
       <c r="C119" t="n">
         <v>52.15649032592773</v>
@@ -3406,7 +3406,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>36.07180786132812</v>
+        <v>36.07181549072266</v>
       </c>
       <c r="C120" t="n">
         <v>50.58206176757812</v>
@@ -3464,7 +3464,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>34.77745819091797</v>
+        <v>34.77747344970703</v>
       </c>
       <c r="C122" t="n">
         <v>48.34923553466797</v>
@@ -3493,7 +3493,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>34.46173858642578</v>
+        <v>34.46175384521484</v>
       </c>
       <c r="C123" t="n">
         <v>47.91030502319336</v>
@@ -3522,7 +3522,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>36.63259887695312</v>
+        <v>36.63259506225586</v>
       </c>
       <c r="C124" t="n">
         <v>50.48664093017578</v>
@@ -3551,7 +3551,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>37.96885681152344</v>
+        <v>37.96884918212891</v>
       </c>
       <c r="C125" t="n">
         <v>52.32824325561523</v>
@@ -3580,7 +3580,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>38.95199584960938</v>
+        <v>38.95198440551758</v>
       </c>
       <c r="C126" t="n">
         <v>53.68320465087891</v>
@@ -3609,7 +3609,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>40.21227645874023</v>
+        <v>40.21228790283203</v>
       </c>
       <c r="C127" t="n">
         <v>54.97137451171875</v>
@@ -3667,7 +3667,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>43.82798385620117</v>
+        <v>43.82796859741211</v>
       </c>
       <c r="C129" t="n">
         <v>59.91412353515625</v>
@@ -3696,7 +3696,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>43.88217926025391</v>
+        <v>43.88217544555664</v>
       </c>
       <c r="C130" t="n">
         <v>59.5515251159668</v>
@@ -3725,7 +3725,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>41.28762817382812</v>
+        <v>41.28762435913086</v>
       </c>
       <c r="C131" t="n">
         <v>56.03053283691406</v>
@@ -3754,7 +3754,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>43.02436065673828</v>
+        <v>43.02437591552734</v>
       </c>
       <c r="C132" t="n">
         <v>58.38740539550781</v>
@@ -3783,7 +3783,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>41.71073150634766</v>
+        <v>41.71072769165039</v>
       </c>
       <c r="C133" t="n">
         <v>56.17366409301758</v>
@@ -3812,7 +3812,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>43.92132568359375</v>
+        <v>43.92132949829102</v>
       </c>
       <c r="C134" t="n">
         <v>59.15076446533203</v>
@@ -3841,7 +3841,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>46.67038726806641</v>
+        <v>46.67038345336914</v>
       </c>
       <c r="C135" t="n">
         <v>62.85305404663086</v>
@@ -3870,7 +3870,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>45.34440612792969</v>
+        <v>45.34441375732422</v>
       </c>
       <c r="C136" t="n">
         <v>60.6297721862793</v>
@@ -3899,7 +3899,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>44.48091888427734</v>
+        <v>44.48089981079102</v>
       </c>
       <c r="C137" t="n">
         <v>59.47518920898438</v>
@@ -3928,7 +3928,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>46.46480941772461</v>
+        <v>46.46481704711914</v>
       </c>
       <c r="C138" t="n">
         <v>62.12786483764648</v>
@@ -3957,7 +3957,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>46.07320022583008</v>
+        <v>46.07320404052734</v>
       </c>
       <c r="C139" t="n">
         <v>61.15457916259766</v>
@@ -4015,7 +4015,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>45.90785980224609</v>
+        <v>45.90786361694336</v>
       </c>
       <c r="C141" t="n">
         <v>60.93511581420898</v>
@@ -4073,7 +4073,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>39.88970947265625</v>
+        <v>39.88970565795898</v>
       </c>
       <c r="C143" t="n">
         <v>52.56679534912109</v>
@@ -4102,7 +4102,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>40.02006149291992</v>
+        <v>40.02004623413086</v>
       </c>
       <c r="C144" t="n">
         <v>52.73854827880859</v>
@@ -4131,7 +4131,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>41.09070205688477</v>
+        <v>41.0906982421875</v>
       </c>
       <c r="C145" t="n">
         <v>53.6927490234375</v>
@@ -4160,7 +4160,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>43.26682281494141</v>
+        <v>43.26681900024414</v>
       </c>
       <c r="C146" t="n">
         <v>56.53625869750977</v>
@@ -4189,7 +4189,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>39.59370422363281</v>
+        <v>39.59369659423828</v>
       </c>
       <c r="C147" t="n">
         <v>51.73664093017578</v>
@@ -4218,7 +4218,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>40.12409973144531</v>
+        <v>40.12410736083984</v>
       </c>
       <c r="C148" t="n">
         <v>51.97518920898438</v>
@@ -4247,7 +4247,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>43.36525726318359</v>
+        <v>43.36526107788086</v>
       </c>
       <c r="C149" t="n">
         <v>56.17366409301758</v>
@@ -4276,7 +4276,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>43.85142517089844</v>
+        <v>43.8514404296875</v>
       </c>
       <c r="C150" t="n">
         <v>56.80343627929688</v>
@@ -4305,7 +4305,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>45.05884552001953</v>
+        <v>45.05884170532227</v>
       </c>
       <c r="C151" t="n">
         <v>57.91984558105469</v>
@@ -4334,7 +4334,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>48.89663696289062</v>
+        <v>48.89664840698242</v>
       </c>
       <c r="C152" t="n">
         <v>62.85305404663086</v>
@@ -4363,7 +4363,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>50.91574859619141</v>
+        <v>50.91575622558594</v>
       </c>
       <c r="C153" t="n">
         <v>65.44847106933594</v>
@@ -4392,7 +4392,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>53.0195198059082</v>
+        <v>53.01950454711914</v>
       </c>
       <c r="C154" t="n">
         <v>67.69084167480469</v>
@@ -4421,7 +4421,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>55.01503372192383</v>
+        <v>55.01502990722656</v>
       </c>
       <c r="C155" t="n">
         <v>70.23854827880859</v>
@@ -4450,7 +4450,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>59.29754638671875</v>
+        <v>59.29752349853516</v>
       </c>
       <c r="C156" t="n">
         <v>75.70610809326172</v>
@@ -4479,7 +4479,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>57.50802230834961</v>
+        <v>57.50802993774414</v>
       </c>
       <c r="C157" t="n">
         <v>72.91030120849609</v>
@@ -4508,7 +4508,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>56.0178108215332</v>
+        <v>56.0178337097168</v>
       </c>
       <c r="C158" t="n">
         <v>71.02098846435547</v>
@@ -4537,7 +4537,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>61.18083953857422</v>
+        <v>61.18082427978516</v>
       </c>
       <c r="C159" t="n">
         <v>77.56679534912109</v>
@@ -4595,7 +4595,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>59.64105606079102</v>
+        <v>59.64105224609375</v>
       </c>
       <c r="C161" t="n">
         <v>75.10496520996094</v>
@@ -4682,7 +4682,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>63.30414199829102</v>
+        <v>63.30415344238281</v>
       </c>
       <c r="C164" t="n">
         <v>79.18893432617188</v>
@@ -4711,7 +4711,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>65.95867919921875</v>
+        <v>65.95866394042969</v>
       </c>
       <c r="C165" t="n">
         <v>82.50954437255859</v>
@@ -4740,7 +4740,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>64.63860321044922</v>
+        <v>64.63858795166016</v>
       </c>
       <c r="C166" t="n">
         <v>80.32442474365234</v>
@@ -4769,7 +4769,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>66.54291534423828</v>
+        <v>66.54288482666016</v>
       </c>
       <c r="C167" t="n">
         <v>82.69084167480469</v>
@@ -4798,7 +4798,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>66.94218444824219</v>
+        <v>66.94216156005859</v>
       </c>
       <c r="C168" t="n">
         <v>83.18701934814453</v>
@@ -4827,7 +4827,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>70.31588745117188</v>
+        <v>70.31587982177734</v>
       </c>
       <c r="C169" t="n">
         <v>86.78434753417969</v>
@@ -4856,7 +4856,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>66.05598449707031</v>
+        <v>66.05596923828125</v>
       </c>
       <c r="C170" t="n">
         <v>81.52671813964844</v>
@@ -4885,7 +4885,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>59.19058990478516</v>
+        <v>59.19060134887695</v>
       </c>
       <c r="C171" t="n">
         <v>73.05343627929688</v>
@@ -4943,7 +4943,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>61.84662628173828</v>
+        <v>61.84662246704102</v>
       </c>
       <c r="C173" t="n">
         <v>75.70610809326172</v>
@@ -4972,7 +4972,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>62.92234802246094</v>
+        <v>62.92235946655273</v>
       </c>
       <c r="C174" t="n">
         <v>77.02290344238281</v>
@@ -5001,7 +5001,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>60.75896453857422</v>
+        <v>60.75896835327148</v>
       </c>
       <c r="C175" t="n">
         <v>73.78816986083984</v>
@@ -5030,7 +5030,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>63.04537963867188</v>
+        <v>63.04538726806641</v>
       </c>
       <c r="C176" t="n">
         <v>76.56488800048828</v>
@@ -5059,7 +5059,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>66.99750518798828</v>
+        <v>66.99751281738281</v>
       </c>
       <c r="C177" t="n">
         <v>81.364501953125</v>
@@ -5088,7 +5088,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>65.64866638183594</v>
+        <v>65.64867401123047</v>
       </c>
       <c r="C178" t="n">
         <v>79.15076446533203</v>
@@ -5117,7 +5117,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>59.52305221557617</v>
+        <v>59.52305603027344</v>
       </c>
       <c r="C179" t="n">
         <v>71.76526641845703</v>
@@ -5146,7 +5146,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>63.62262725830078</v>
+        <v>63.62264251708984</v>
       </c>
       <c r="C180" t="n">
         <v>76.70801544189453</v>
@@ -5175,7 +5175,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>65.24978637695312</v>
+        <v>65.24980163574219</v>
       </c>
       <c r="C181" t="n">
         <v>78.05343627929688</v>
@@ -5204,7 +5204,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>61.47679138183594</v>
+        <v>61.47678756713867</v>
       </c>
       <c r="C182" t="n">
         <v>73.54007720947266</v>
@@ -5291,7 +5291,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>59.94888687133789</v>
+        <v>59.94889450073242</v>
       </c>
       <c r="C185" t="n">
         <v>71.08778381347656</v>
@@ -5320,7 +5320,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>61.06738662719727</v>
+        <v>61.0673828125</v>
       </c>
       <c r="C186" t="n">
         <v>72.41412353515625</v>
@@ -5349,7 +5349,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>66.14777374267578</v>
+        <v>66.14778900146484</v>
       </c>
       <c r="C187" t="n">
         <v>77.76999664306641</v>
@@ -5378,7 +5378,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>65.38230133056641</v>
+        <v>65.38227844238281</v>
       </c>
       <c r="C188" t="n">
         <v>76.87000274658203</v>
@@ -5436,7 +5436,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>64.45784759521484</v>
+        <v>64.45783233642578</v>
       </c>
       <c r="C190" t="n">
         <v>75.11000061035156</v>
@@ -5465,7 +5465,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>75.56267547607422</v>
+        <v>75.56268310546875</v>
       </c>
       <c r="C191" t="n">
         <v>88.05000305175781</v>
@@ -5494,7 +5494,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>64.28620147705078</v>
+        <v>64.28619384765625</v>
       </c>
       <c r="C192" t="n">
         <v>74.91000366210938</v>
@@ -5552,7 +5552,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>70.58779907226562</v>
+        <v>70.58782196044922</v>
       </c>
       <c r="C194" t="n">
         <v>81.48000335693359</v>
@@ -5581,7 +5581,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>66.34284973144531</v>
+        <v>66.34283447265625</v>
       </c>
       <c r="C195" t="n">
         <v>76.58000183105469</v>
@@ -5639,7 +5639,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>77.51744842529297</v>
+        <v>77.51744079589844</v>
       </c>
       <c r="C197" t="n">
         <v>88.69000244140625</v>
@@ -5668,7 +5668,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>80.43669128417969</v>
+        <v>80.43669891357422</v>
       </c>
       <c r="C198" t="n">
         <v>92.02999877929688</v>
@@ -5697,7 +5697,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>80.33717346191406</v>
+        <v>80.33718872070312</v>
       </c>
       <c r="C199" t="n">
         <v>91.16999816894531</v>
@@ -5726,7 +5726,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>78.72461700439453</v>
+        <v>78.724609375</v>
       </c>
       <c r="C200" t="n">
         <v>89.33999633789062</v>
@@ -5755,7 +5755,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>75.217529296875</v>
+        <v>75.21752166748047</v>
       </c>
       <c r="C201" t="n">
         <v>85.36000061035156</v>
@@ -5813,7 +5813,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>89.89430236816406</v>
+        <v>89.89431762695312</v>
       </c>
       <c r="C203" t="n">
         <v>101.1999969482422</v>
@@ -5842,7 +5842,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>97.81780242919922</v>
+        <v>97.81781005859375</v>
       </c>
       <c r="C204" t="n">
         <v>110.120002746582</v>
@@ -5871,7 +5871,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>99.20807647705078</v>
+        <v>99.20806884765625</v>
       </c>
       <c r="C205" t="n">
         <v>110.9499969482422</v>
@@ -5900,7 +5900,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>96.042724609375</v>
+        <v>96.04270172119141</v>
       </c>
       <c r="C206" t="n">
         <v>107.4100036621094</v>
@@ -5958,7 +5958,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>95.79202270507812</v>
+        <v>95.79203033447266</v>
       </c>
       <c r="C208" t="n">
         <v>106.3899993896484</v>
@@ -6016,7 +6016,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>99.41157531738281</v>
+        <v>99.41158294677734</v>
       </c>
       <c r="C210" t="n">
         <v>110.4100036621094</v>
@@ -6045,7 +6045,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>104.5896530151367</v>
+        <v>104.5896606445312</v>
       </c>
       <c r="C211" t="n">
         <v>115.3899993896484</v>
@@ -6074,7 +6074,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>96.66770172119141</v>
+        <v>96.667724609375</v>
       </c>
       <c r="C212" t="n">
         <v>106.6500015258789</v>
@@ -6103,7 +6103,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>98.77964019775391</v>
+        <v>98.77963256835938</v>
       </c>
       <c r="C213" t="n">
         <v>108.9800033569336</v>
@@ -6132,7 +6132,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>93.95017242431641</v>
+        <v>93.95018005371094</v>
       </c>
       <c r="C214" t="n">
         <v>102.9499969482422</v>
@@ -6161,7 +6161,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>93.72203063964844</v>
+        <v>93.72203826904297</v>
       </c>
       <c r="C215" t="n">
         <v>102.6999969482422</v>
@@ -6190,7 +6190,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>93.52127075195312</v>
+        <v>93.52127838134766</v>
       </c>
       <c r="C216" t="n">
         <v>102.4800033569336</v>
@@ -6219,7 +6219,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>100.2099456787109</v>
+        <v>100.2099380493164</v>
       </c>
       <c r="C217" t="n">
         <v>109.0199966430664</v>
@@ -6277,7 +6277,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>116.8748321533203</v>
+        <v>116.8748397827148</v>
       </c>
       <c r="C219" t="n">
         <v>127.1500015258789</v>
@@ -6306,7 +6306,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>122.056282043457</v>
+        <v>122.0562896728516</v>
       </c>
       <c r="C220" t="n">
         <v>131.9499969482422</v>
@@ -6393,7 +6393,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>115.2024688720703</v>
+        <v>115.2024765014648</v>
       </c>
       <c r="C223" t="n">
         <v>123.8000030517578</v>
@@ -6422,7 +6422,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>105.2734603881836</v>
+        <v>105.2734756469727</v>
       </c>
       <c r="C224" t="n">
         <v>113.129997253418</v>
@@ -6480,7 +6480,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>106.3806076049805</v>
+        <v>106.3806228637695</v>
       </c>
       <c r="C226" t="n">
         <v>113.5599975585938</v>
@@ -6509,7 +6509,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>95.85121154785156</v>
+        <v>95.85121917724609</v>
       </c>
       <c r="C227" t="n">
         <v>102.3199996948242</v>
@@ -6567,7 +6567,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>93.93673706054688</v>
+        <v>93.93672943115234</v>
       </c>
       <c r="C229" t="n">
         <v>99.48000335693359</v>
@@ -6596,7 +6596,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>93.31351470947266</v>
+        <v>93.31350708007812</v>
       </c>
       <c r="C230" t="n">
         <v>98.81999969482422</v>
@@ -6625,7 +6625,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>87.10959625244141</v>
+        <v>87.10960388183594</v>
       </c>
       <c r="C231" t="n">
         <v>92.25</v>
@@ -6654,7 +6654,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>85.49058532714844</v>
+        <v>85.49059295654297</v>
       </c>
       <c r="C232" t="n">
         <v>89.76000213623047</v>
@@ -6683,7 +6683,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>81.14746856689453</v>
+        <v>81.14748382568359</v>
       </c>
       <c r="C233" t="n">
         <v>85.19999694824219</v>
@@ -6828,7 +6828,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>81.53579711914062</v>
+        <v>81.53578948974609</v>
       </c>
       <c r="C238" t="n">
         <v>83.93000030517578</v>
@@ -6857,7 +6857,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>83.52731323242188</v>
+        <v>83.52732086181641</v>
       </c>
       <c r="C239" t="n">
         <v>85.98000335693359</v>
@@ -6886,7 +6886,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>101.839599609375</v>
+        <v>101.8395843505859</v>
       </c>
       <c r="C240" t="n">
         <v>104.8300018310547</v>
